--- a/Team-Data/2014-15/4-3-2014-15.xlsx
+++ b/Team-Data/2014-15/4-3-2014-15.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>5</v>
       </c>
       <c r="AD2" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="AE2" t="n">
         <v>2</v>
@@ -778,13 +845,13 @@
         <v>24</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AR2" t="n">
         <v>30</v>
       </c>
       <c r="AS2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT2" t="n">
         <v>28</v>
@@ -799,7 +866,7 @@
         <v>5</v>
       </c>
       <c r="AX2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY2" t="n">
         <v>18</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-3-2014-15</t>
+          <t>2015-04-03</t>
         </is>
       </c>
     </row>
@@ -843,16 +910,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E3" t="n">
         <v>34</v>
       </c>
       <c r="F3" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G3" t="n">
-        <v>0.447</v>
+        <v>0.453</v>
       </c>
       <c r="H3" t="n">
         <v>48.5</v>
@@ -879,19 +946,19 @@
         <v>15.4</v>
       </c>
       <c r="P3" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.753</v>
+        <v>0.751</v>
       </c>
       <c r="R3" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="S3" t="n">
         <v>32.9</v>
       </c>
       <c r="T3" t="n">
-        <v>44</v>
+        <v>44.1</v>
       </c>
       <c r="U3" t="n">
         <v>24.3</v>
@@ -909,7 +976,7 @@
         <v>5.3</v>
       </c>
       <c r="Z3" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AA3" t="n">
         <v>18.7</v>
@@ -918,25 +985,25 @@
         <v>100.9</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.7</v>
+        <v>-0.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AE3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF3" t="n">
         <v>18</v>
       </c>
-      <c r="AF3" t="n">
-        <v>20</v>
-      </c>
       <c r="AG3" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AH3" t="n">
         <v>12</v>
       </c>
       <c r="AI3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ3" t="n">
         <v>1</v>
@@ -948,7 +1015,7 @@
         <v>13</v>
       </c>
       <c r="AM3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AN3" t="n">
         <v>27</v>
@@ -960,19 +1027,19 @@
         <v>27</v>
       </c>
       <c r="AQ3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AR3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AS3" t="n">
         <v>11</v>
       </c>
       <c r="AT3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV3" t="n">
         <v>10</v>
@@ -984,7 +1051,7 @@
         <v>30</v>
       </c>
       <c r="AY3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ3" t="n">
         <v>22</v>
@@ -993,7 +1060,7 @@
         <v>28</v>
       </c>
       <c r="BB3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BC3" t="n">
         <v>19</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-3-2014-15</t>
+          <t>2015-04-03</t>
         </is>
       </c>
     </row>
@@ -1025,34 +1092,34 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E4" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F4" t="n">
         <v>40</v>
       </c>
       <c r="G4" t="n">
-        <v>0.467</v>
+        <v>0.459</v>
       </c>
       <c r="H4" t="n">
         <v>48.7</v>
       </c>
       <c r="I4" t="n">
-        <v>37.4</v>
+        <v>37.3</v>
       </c>
       <c r="J4" t="n">
-        <v>82.8</v>
+        <v>82.7</v>
       </c>
       <c r="K4" t="n">
-        <v>0.452</v>
+        <v>0.451</v>
       </c>
       <c r="L4" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="M4" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="N4" t="n">
         <v>0.328</v>
@@ -1061,16 +1128,16 @@
         <v>16.6</v>
       </c>
       <c r="P4" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.748</v>
+        <v>0.749</v>
       </c>
       <c r="R4" t="n">
         <v>10.1</v>
       </c>
       <c r="S4" t="n">
-        <v>32.1</v>
+        <v>32.2</v>
       </c>
       <c r="T4" t="n">
         <v>42.2</v>
@@ -1079,7 +1146,7 @@
         <v>20.8</v>
       </c>
       <c r="V4" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="W4" t="n">
         <v>7</v>
@@ -1088,7 +1155,7 @@
         <v>4.2</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Z4" t="n">
         <v>19.6</v>
@@ -1097,13 +1164,13 @@
         <v>20.1</v>
       </c>
       <c r="AB4" t="n">
-        <v>97.90000000000001</v>
+        <v>97.7</v>
       </c>
       <c r="AC4" t="n">
-        <v>-2.8</v>
+        <v>-2.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="AE4" t="n">
         <v>17</v>
@@ -1115,16 +1182,16 @@
         <v>17</v>
       </c>
       <c r="AH4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AJ4" t="n">
         <v>18</v>
       </c>
       <c r="AK4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL4" t="n">
         <v>24</v>
@@ -1136,25 +1203,25 @@
         <v>26</v>
       </c>
       <c r="AO4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP4" t="n">
         <v>17</v>
       </c>
       <c r="AQ4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR4" t="n">
         <v>24</v>
       </c>
       <c r="AS4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT4" t="n">
         <v>22</v>
       </c>
       <c r="AU4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AV4" t="n">
         <v>12</v>
@@ -1175,7 +1242,7 @@
         <v>18</v>
       </c>
       <c r="BB4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC4" t="n">
         <v>23</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-3-2014-15</t>
+          <t>2015-04-03</t>
         </is>
       </c>
     </row>
@@ -1207,37 +1274,37 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E5" t="n">
         <v>32</v>
       </c>
       <c r="F5" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G5" t="n">
-        <v>0.427</v>
+        <v>0.432</v>
       </c>
       <c r="H5" t="n">
         <v>48.6</v>
       </c>
       <c r="I5" t="n">
-        <v>35.9</v>
+        <v>36</v>
       </c>
       <c r="J5" t="n">
         <v>84.8</v>
       </c>
       <c r="K5" t="n">
-        <v>0.423</v>
+        <v>0.424</v>
       </c>
       <c r="L5" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="M5" t="n">
         <v>18.7</v>
       </c>
       <c r="N5" t="n">
-        <v>0.317</v>
+        <v>0.318</v>
       </c>
       <c r="O5" t="n">
         <v>17.3</v>
@@ -1246,7 +1313,7 @@
         <v>23.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.748</v>
+        <v>0.749</v>
       </c>
       <c r="R5" t="n">
         <v>10</v>
@@ -1258,13 +1325,13 @@
         <v>44.4</v>
       </c>
       <c r="U5" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="V5" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="W5" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="X5" t="n">
         <v>5.6</v>
@@ -1279,22 +1346,22 @@
         <v>21</v>
       </c>
       <c r="AB5" t="n">
-        <v>94.90000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>-2.1</v>
+        <v>-1.9</v>
       </c>
       <c r="AD5" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="AE5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF5" t="n">
         <v>21</v>
       </c>
       <c r="AG5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH5" t="n">
         <v>5</v>
@@ -1309,7 +1376,7 @@
         <v>29</v>
       </c>
       <c r="AL5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AM5" t="n">
         <v>25</v>
@@ -1318,13 +1385,13 @@
         <v>30</v>
       </c>
       <c r="AO5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AP5" t="n">
         <v>14</v>
       </c>
       <c r="AQ5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AR5" t="n">
         <v>25</v>
@@ -1336,7 +1403,7 @@
         <v>8</v>
       </c>
       <c r="AU5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AV5" t="n">
         <v>1</v>
@@ -1351,7 +1418,7 @@
         <v>20</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA5" t="n">
         <v>7</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-3-2014-15</t>
+          <t>2015-04-03</t>
         </is>
       </c>
     </row>
@@ -1389,40 +1456,40 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E6" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F6" t="n">
         <v>30</v>
       </c>
       <c r="G6" t="n">
-        <v>0.605</v>
+        <v>0.6</v>
       </c>
       <c r="H6" t="n">
         <v>48.5</v>
       </c>
       <c r="I6" t="n">
-        <v>36.6</v>
+        <v>36.7</v>
       </c>
       <c r="J6" t="n">
         <v>82.8</v>
       </c>
       <c r="K6" t="n">
-        <v>0.442</v>
+        <v>0.443</v>
       </c>
       <c r="L6" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="M6" t="n">
         <v>22</v>
       </c>
       <c r="N6" t="n">
-        <v>0.352</v>
+        <v>0.354</v>
       </c>
       <c r="O6" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="P6" t="n">
         <v>25.3</v>
@@ -1431,28 +1498,28 @@
         <v>0.785</v>
       </c>
       <c r="R6" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="S6" t="n">
-        <v>33.9</v>
+        <v>34</v>
       </c>
       <c r="T6" t="n">
         <v>45.7</v>
       </c>
       <c r="U6" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="V6" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="W6" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="X6" t="n">
         <v>5.9</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Z6" t="n">
         <v>18.4</v>
@@ -1461,19 +1528,19 @@
         <v>21.3</v>
       </c>
       <c r="AB6" t="n">
-        <v>100.8</v>
+        <v>101</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AE6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF6" t="n">
         <v>9</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>10</v>
       </c>
       <c r="AG6" t="n">
         <v>10</v>
@@ -1497,7 +1564,7 @@
         <v>16</v>
       </c>
       <c r="AN6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO6" t="n">
         <v>2</v>
@@ -1509,10 +1576,10 @@
         <v>3</v>
       </c>
       <c r="AR6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS6" t="n">
         <v>6</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>7</v>
       </c>
       <c r="AT6" t="n">
         <v>3</v>
@@ -1530,7 +1597,7 @@
         <v>5</v>
       </c>
       <c r="AY6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ6" t="n">
         <v>3</v>
@@ -1539,7 +1606,7 @@
         <v>5</v>
       </c>
       <c r="BB6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BC6" t="n">
         <v>11</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-3-2014-15</t>
+          <t>2015-04-03</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1749,7 @@
         <v>6</v>
       </c>
       <c r="AO7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AP7" t="n">
         <v>9</v>
@@ -1703,7 +1770,7 @@
         <v>12</v>
       </c>
       <c r="AV7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW7" t="n">
         <v>19</v>
@@ -1715,13 +1782,13 @@
         <v>12</v>
       </c>
       <c r="AZ7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC7" t="n">
         <v>4</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-3-2014-15</t>
+          <t>2015-04-03</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E8" t="n">
         <v>46</v>
       </c>
       <c r="F8" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G8" t="n">
-        <v>0.613</v>
+        <v>0.605</v>
       </c>
       <c r="H8" t="n">
         <v>48.4</v>
@@ -1771,16 +1838,16 @@
         <v>39.5</v>
       </c>
       <c r="J8" t="n">
-        <v>85.7</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>0.461</v>
+        <v>0.462</v>
       </c>
       <c r="L8" t="n">
         <v>9</v>
       </c>
       <c r="M8" t="n">
-        <v>25.8</v>
+        <v>25.7</v>
       </c>
       <c r="N8" t="n">
         <v>0.351</v>
@@ -1789,25 +1856,25 @@
         <v>16.5</v>
       </c>
       <c r="P8" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.751</v>
+        <v>0.752</v>
       </c>
       <c r="R8" t="n">
         <v>10.4</v>
       </c>
       <c r="S8" t="n">
-        <v>31.7</v>
+        <v>31.6</v>
       </c>
       <c r="T8" t="n">
-        <v>42.1</v>
+        <v>42</v>
       </c>
       <c r="U8" t="n">
         <v>22.5</v>
       </c>
       <c r="V8" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="W8" t="n">
         <v>8.199999999999999</v>
@@ -1822,7 +1889,7 @@
         <v>20</v>
       </c>
       <c r="AA8" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="AB8" t="n">
         <v>104.5</v>
@@ -1831,7 +1898,7 @@
         <v>3.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="AE8" t="n">
         <v>9</v>
@@ -1843,7 +1910,7 @@
         <v>9</v>
       </c>
       <c r="AH8" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AI8" t="n">
         <v>2</v>
@@ -1867,16 +1934,16 @@
         <v>21</v>
       </c>
       <c r="AP8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR8" t="n">
         <v>19</v>
       </c>
       <c r="AS8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT8" t="n">
         <v>24</v>
@@ -1891,7 +1958,7 @@
         <v>8</v>
       </c>
       <c r="AX8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY8" t="n">
         <v>4</v>
@@ -1906,7 +1973,7 @@
         <v>3</v>
       </c>
       <c r="BC8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-3-2014-15</t>
+          <t>2015-04-03</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E9" t="n">
         <v>28</v>
       </c>
       <c r="F9" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G9" t="n">
-        <v>0.368</v>
+        <v>0.373</v>
       </c>
       <c r="H9" t="n">
         <v>48.4</v>
@@ -1962,31 +2029,31 @@
         <v>7.9</v>
       </c>
       <c r="M9" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="N9" t="n">
         <v>0.322</v>
       </c>
       <c r="O9" t="n">
-        <v>17.5</v>
+        <v>17.7</v>
       </c>
       <c r="P9" t="n">
-        <v>24</v>
+        <v>24.2</v>
       </c>
       <c r="Q9" t="n">
         <v>0.731</v>
       </c>
       <c r="R9" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="S9" t="n">
-        <v>32.4</v>
+        <v>32.5</v>
       </c>
       <c r="T9" t="n">
-        <v>44.4</v>
+        <v>44.5</v>
       </c>
       <c r="U9" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="V9" t="n">
         <v>14.1</v>
@@ -1998,22 +2065,22 @@
         <v>4.7</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="Z9" t="n">
         <v>22.7</v>
       </c>
       <c r="AA9" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>100.2</v>
+        <v>100.3</v>
       </c>
       <c r="AC9" t="n">
-        <v>-3.8</v>
+        <v>-3.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AE9" t="n">
         <v>24</v>
@@ -2025,10 +2092,10 @@
         <v>24</v>
       </c>
       <c r="AH9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI9" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AJ9" t="n">
         <v>3</v>
@@ -2040,28 +2107,28 @@
         <v>14</v>
       </c>
       <c r="AM9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AN9" t="n">
         <v>29</v>
       </c>
       <c r="AO9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AP9" t="n">
         <v>8</v>
       </c>
       <c r="AQ9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AR9" t="n">
         <v>3</v>
       </c>
       <c r="AS9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AT9" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AU9" t="n">
         <v>16</v>
@@ -2073,7 +2140,7 @@
         <v>15</v>
       </c>
       <c r="AX9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY9" t="n">
         <v>29</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-3-2014-15</t>
+          <t>2015-04-03</t>
         </is>
       </c>
     </row>
@@ -2117,25 +2184,25 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E10" t="n">
         <v>29</v>
       </c>
       <c r="F10" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G10" t="n">
-        <v>0.382</v>
+        <v>0.387</v>
       </c>
       <c r="H10" t="n">
         <v>48.4</v>
       </c>
       <c r="I10" t="n">
-        <v>36.8</v>
+        <v>36.9</v>
       </c>
       <c r="J10" t="n">
-        <v>86.09999999999999</v>
+        <v>86.3</v>
       </c>
       <c r="K10" t="n">
         <v>0.428</v>
@@ -2147,16 +2214,16 @@
         <v>25</v>
       </c>
       <c r="N10" t="n">
-        <v>0.336</v>
+        <v>0.337</v>
       </c>
       <c r="O10" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="P10" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.706</v>
+        <v>0.705</v>
       </c>
       <c r="R10" t="n">
         <v>13</v>
@@ -2165,19 +2232,19 @@
         <v>32.2</v>
       </c>
       <c r="T10" t="n">
-        <v>45.1</v>
+        <v>45.2</v>
       </c>
       <c r="U10" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="V10" t="n">
-        <v>13.4</v>
+        <v>13.3</v>
       </c>
       <c r="W10" t="n">
         <v>7.6</v>
       </c>
       <c r="X10" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Y10" t="n">
         <v>4.9</v>
@@ -2186,16 +2253,16 @@
         <v>18.9</v>
       </c>
       <c r="AA10" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>98</v>
+        <v>98.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>-1.6</v>
+        <v>-1.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AE10" t="n">
         <v>23</v>
@@ -2207,16 +2274,16 @@
         <v>23</v>
       </c>
       <c r="AH10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI10" t="n">
         <v>21</v>
       </c>
       <c r="AJ10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AK10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL10" t="n">
         <v>10</v>
@@ -2249,22 +2316,22 @@
         <v>17</v>
       </c>
       <c r="AV10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW10" t="n">
         <v>16</v>
       </c>
       <c r="AX10" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AY10" t="n">
         <v>17</v>
       </c>
       <c r="AZ10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BB10" t="n">
         <v>20</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-3-2014-15</t>
+          <t>2015-04-03</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>10.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2410,7 +2477,7 @@
         <v>1</v>
       </c>
       <c r="AO11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP11" t="n">
         <v>26</v>
@@ -2437,7 +2504,7 @@
         <v>4</v>
       </c>
       <c r="AX11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY11" t="n">
         <v>2</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-3-2014-15</t>
+          <t>2015-04-03</t>
         </is>
       </c>
     </row>
@@ -2481,16 +2548,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F12" t="n">
         <v>24</v>
       </c>
       <c r="G12" t="n">
-        <v>0.68</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="H12" t="n">
         <v>48.3</v>
@@ -2499,7 +2566,7 @@
         <v>37</v>
       </c>
       <c r="J12" t="n">
-        <v>83.90000000000001</v>
+        <v>83.8</v>
       </c>
       <c r="K12" t="n">
         <v>0.441</v>
@@ -2508,19 +2575,19 @@
         <v>11.5</v>
       </c>
       <c r="M12" t="n">
-        <v>33.2</v>
+        <v>33.1</v>
       </c>
       <c r="N12" t="n">
-        <v>0.347</v>
+        <v>0.348</v>
       </c>
       <c r="O12" t="n">
-        <v>17.9</v>
+        <v>18.1</v>
       </c>
       <c r="P12" t="n">
-        <v>24.7</v>
+        <v>25.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.722</v>
+        <v>0.721</v>
       </c>
       <c r="R12" t="n">
         <v>11.9</v>
@@ -2535,7 +2602,7 @@
         <v>22.3</v>
       </c>
       <c r="V12" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="W12" t="n">
         <v>9.5</v>
@@ -2544,34 +2611,34 @@
         <v>4.8</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AB12" t="n">
         <v>103.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="AE12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF12" t="n">
         <v>3</v>
       </c>
       <c r="AG12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AI12" t="n">
         <v>20</v>
@@ -2589,16 +2656,16 @@
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AQ12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AR12" t="n">
         <v>5</v>
@@ -2607,7 +2674,7 @@
         <v>21</v>
       </c>
       <c r="AT12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU12" t="n">
         <v>9</v>
@@ -2622,19 +2689,19 @@
         <v>11</v>
       </c>
       <c r="AY12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ12" t="n">
         <v>27</v>
       </c>
       <c r="BA12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BB12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-3-2014-15</t>
+          <t>2015-04-03</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E13" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F13" t="n">
         <v>43</v>
       </c>
       <c r="G13" t="n">
-        <v>0.434</v>
+        <v>0.427</v>
       </c>
       <c r="H13" t="n">
         <v>48.3</v>
@@ -2690,37 +2757,37 @@
         <v>7.3</v>
       </c>
       <c r="M13" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="N13" t="n">
-        <v>0.349</v>
+        <v>0.347</v>
       </c>
       <c r="O13" t="n">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
       <c r="P13" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.759</v>
+        <v>0.76</v>
       </c>
       <c r="R13" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="S13" t="n">
-        <v>34.3</v>
+        <v>34.2</v>
       </c>
       <c r="T13" t="n">
-        <v>44.5</v>
+        <v>44.4</v>
       </c>
       <c r="U13" t="n">
         <v>21.3</v>
       </c>
       <c r="V13" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="W13" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="X13" t="n">
         <v>4.5</v>
@@ -2732,28 +2799,28 @@
         <v>21.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AB13" t="n">
         <v>96.90000000000001</v>
       </c>
       <c r="AC13" t="n">
-        <v>-0.3</v>
+        <v>-0.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AE13" t="n">
         <v>21</v>
       </c>
       <c r="AF13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI13" t="n">
         <v>25</v>
@@ -2771,16 +2838,16 @@
         <v>18</v>
       </c>
       <c r="AN13" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AO13" t="n">
         <v>17</v>
       </c>
       <c r="AP13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AQ13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR13" t="n">
         <v>23</v>
@@ -2789,28 +2856,28 @@
         <v>5</v>
       </c>
       <c r="AT13" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AU13" t="n">
         <v>18</v>
       </c>
       <c r="AV13" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AW13" t="n">
         <v>28</v>
       </c>
       <c r="AX13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY13" t="n">
         <v>15</v>
       </c>
       <c r="AZ13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BB13" t="n">
         <v>24</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-3-2014-15</t>
+          <t>2015-04-03</t>
         </is>
       </c>
     </row>
@@ -2938,10 +3005,10 @@
         <v>29</v>
       </c>
       <c r="AI14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AK14" t="n">
         <v>2</v>
@@ -2959,7 +3026,7 @@
         <v>8</v>
       </c>
       <c r="AP14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ14" t="n">
         <v>28</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-3-2014-15</t>
+          <t>2015-04-03</t>
         </is>
       </c>
     </row>
@@ -3048,10 +3115,10 @@
         <v>85.90000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>0.437</v>
+        <v>0.436</v>
       </c>
       <c r="L15" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="M15" t="n">
         <v>18.8</v>
@@ -3060,22 +3127,22 @@
         <v>0.344</v>
       </c>
       <c r="O15" t="n">
-        <v>17.2</v>
+        <v>17.5</v>
       </c>
       <c r="P15" t="n">
-        <v>23.2</v>
+        <v>23.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.742</v>
+        <v>0.745</v>
       </c>
       <c r="R15" t="n">
         <v>11.6</v>
       </c>
       <c r="S15" t="n">
-        <v>32.5</v>
+        <v>32.3</v>
       </c>
       <c r="T15" t="n">
-        <v>44.1</v>
+        <v>44</v>
       </c>
       <c r="U15" t="n">
         <v>20.9</v>
@@ -3084,7 +3151,7 @@
         <v>13.1</v>
       </c>
       <c r="W15" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X15" t="n">
         <v>4.6</v>
@@ -3093,19 +3160,19 @@
         <v>4.8</v>
       </c>
       <c r="Z15" t="n">
-        <v>20.9</v>
+        <v>21.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>19.3</v>
+        <v>19.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>98.7</v>
+        <v>98.8</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.1</v>
+        <v>-6</v>
       </c>
       <c r="AD15" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
@@ -3135,13 +3202,13 @@
         <v>24</v>
       </c>
       <c r="AN15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AP15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AQ15" t="n">
         <v>22</v>
@@ -3150,10 +3217,10 @@
         <v>9</v>
       </c>
       <c r="AS15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AT15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU15" t="n">
         <v>20</v>
@@ -3162,7 +3229,7 @@
         <v>5</v>
       </c>
       <c r="AW15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX15" t="n">
         <v>18</v>
@@ -3171,16 +3238,16 @@
         <v>16</v>
       </c>
       <c r="AZ15" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BA15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB15" t="n">
         <v>17</v>
       </c>
       <c r="BC15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-3-2014-15</t>
+          <t>2015-04-03</t>
         </is>
       </c>
     </row>
@@ -3209,16 +3276,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E16" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F16" t="n">
         <v>24</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="H16" t="n">
         <v>48.6</v>
@@ -3239,28 +3306,28 @@
         <v>15.3</v>
       </c>
       <c r="N16" t="n">
-        <v>0.343</v>
+        <v>0.346</v>
       </c>
       <c r="O16" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="P16" t="n">
         <v>22.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.775</v>
+        <v>0.776</v>
       </c>
       <c r="R16" t="n">
         <v>10.3</v>
       </c>
       <c r="S16" t="n">
-        <v>32.2</v>
+        <v>32.1</v>
       </c>
       <c r="T16" t="n">
         <v>42.4</v>
       </c>
       <c r="U16" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="V16" t="n">
         <v>13.3</v>
@@ -3272,7 +3339,7 @@
         <v>4.3</v>
       </c>
       <c r="Y16" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Z16" t="n">
         <v>19.1</v>
@@ -3287,16 +3354,16 @@
         <v>3.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AE16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF16" t="n">
         <v>3</v>
       </c>
       <c r="AG16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH16" t="n">
         <v>6</v>
@@ -3305,7 +3372,7 @@
         <v>13</v>
       </c>
       <c r="AJ16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK16" t="n">
         <v>9</v>
@@ -3317,7 +3384,7 @@
         <v>29</v>
       </c>
       <c r="AN16" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AO16" t="n">
         <v>9</v>
@@ -3329,10 +3396,10 @@
         <v>6</v>
       </c>
       <c r="AR16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS16" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AT16" t="n">
         <v>21</v>
@@ -3341,28 +3408,28 @@
         <v>14</v>
       </c>
       <c r="AV16" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW16" t="n">
         <v>6</v>
       </c>
-      <c r="AW16" t="n">
-        <v>7</v>
-      </c>
       <c r="AX16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY16" t="n">
         <v>21</v>
       </c>
       <c r="AZ16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB16" t="n">
         <v>18</v>
       </c>
       <c r="BC16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-3-2014-15</t>
+          <t>2015-04-03</t>
         </is>
       </c>
     </row>
@@ -3469,10 +3536,10 @@
         <v>-2.5</v>
       </c>
       <c r="AD17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE17" t="n">
         <v>17</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>18</v>
       </c>
       <c r="AF17" t="n">
         <v>18</v>
@@ -3490,7 +3557,7 @@
         <v>30</v>
       </c>
       <c r="AK17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL17" t="n">
         <v>20</v>
@@ -3502,7 +3569,7 @@
         <v>21</v>
       </c>
       <c r="AO17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP17" t="n">
         <v>11</v>
@@ -3523,13 +3590,13 @@
         <v>29</v>
       </c>
       <c r="AV17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW17" t="n">
         <v>10</v>
       </c>
       <c r="AX17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY17" t="n">
         <v>8</v>
@@ -3538,7 +3605,7 @@
         <v>14</v>
       </c>
       <c r="BA17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BB17" t="n">
         <v>28</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-3-2014-15</t>
+          <t>2015-04-03</t>
         </is>
       </c>
     </row>
@@ -3573,34 +3640,34 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E18" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F18" t="n">
         <v>38</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5</v>
+        <v>0.493</v>
       </c>
       <c r="H18" t="n">
         <v>48.7</v>
       </c>
       <c r="I18" t="n">
-        <v>37.4</v>
+        <v>37.3</v>
       </c>
       <c r="J18" t="n">
         <v>81.8</v>
       </c>
       <c r="K18" t="n">
-        <v>0.457</v>
+        <v>0.456</v>
       </c>
       <c r="L18" t="n">
         <v>6.7</v>
       </c>
       <c r="M18" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="N18" t="n">
         <v>0.365</v>
@@ -3612,19 +3679,19 @@
         <v>21.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.765</v>
+        <v>0.766</v>
       </c>
       <c r="R18" t="n">
         <v>10.7</v>
       </c>
       <c r="S18" t="n">
-        <v>31.5</v>
+        <v>31.4</v>
       </c>
       <c r="T18" t="n">
-        <v>42.2</v>
+        <v>42.1</v>
       </c>
       <c r="U18" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="V18" t="n">
         <v>16.8</v>
@@ -3639,40 +3706,40 @@
         <v>4.7</v>
       </c>
       <c r="Z18" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="AA18" t="n">
         <v>20.1</v>
       </c>
       <c r="AB18" t="n">
-        <v>97.8</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AE18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF18" t="n">
         <v>15</v>
       </c>
       <c r="AG18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH18" t="n">
         <v>4</v>
       </c>
       <c r="AI18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ18" t="n">
         <v>26</v>
       </c>
       <c r="AK18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AL18" t="n">
         <v>23</v>
@@ -3717,16 +3784,16 @@
         <v>14</v>
       </c>
       <c r="AZ18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BA18" t="n">
         <v>17</v>
       </c>
       <c r="BB18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-3-2014-15</t>
+          <t>2015-04-03</t>
         </is>
       </c>
     </row>
@@ -3755,61 +3822,61 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E19" t="n">
         <v>16</v>
       </c>
       <c r="F19" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G19" t="n">
-        <v>0.211</v>
+        <v>0.213</v>
       </c>
       <c r="H19" t="n">
         <v>48.3</v>
       </c>
       <c r="I19" t="n">
-        <v>36.5</v>
+        <v>36.6</v>
       </c>
       <c r="J19" t="n">
-        <v>83.3</v>
+        <v>83.5</v>
       </c>
       <c r="K19" t="n">
         <v>0.438</v>
       </c>
       <c r="L19" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="M19" t="n">
         <v>14.8</v>
       </c>
       <c r="N19" t="n">
-        <v>0.333</v>
+        <v>0.335</v>
       </c>
       <c r="O19" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="P19" t="n">
-        <v>25.5</v>
+        <v>25.4</v>
       </c>
       <c r="Q19" t="n">
         <v>0.773</v>
       </c>
       <c r="R19" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="S19" t="n">
         <v>29.4</v>
       </c>
       <c r="T19" t="n">
-        <v>41.1</v>
+        <v>41.2</v>
       </c>
       <c r="U19" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="V19" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="W19" t="n">
         <v>8.199999999999999</v>
@@ -3818,7 +3885,7 @@
         <v>3.9</v>
       </c>
       <c r="Y19" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Z19" t="n">
         <v>19</v>
@@ -3827,13 +3894,13 @@
         <v>21.3</v>
       </c>
       <c r="AB19" t="n">
-        <v>97.59999999999999</v>
+        <v>97.7</v>
       </c>
       <c r="AC19" t="n">
-        <v>-8.4</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="AD19" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AE19" t="n">
         <v>29</v>
@@ -3845,13 +3912,13 @@
         <v>29</v>
       </c>
       <c r="AH19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AJ19" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AK19" t="n">
         <v>24</v>
@@ -3872,10 +3939,10 @@
         <v>2</v>
       </c>
       <c r="AQ19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AR19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AS19" t="n">
         <v>30</v>
@@ -3887,7 +3954,7 @@
         <v>15</v>
       </c>
       <c r="AV19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW19" t="n">
         <v>9</v>
@@ -3899,13 +3966,13 @@
         <v>27</v>
       </c>
       <c r="AZ19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BB19" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BC19" t="n">
         <v>28</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-3-2014-15</t>
+          <t>2015-04-03</t>
         </is>
       </c>
     </row>
@@ -3952,55 +4019,55 @@
         <v>48.3</v>
       </c>
       <c r="I20" t="n">
-        <v>37.9</v>
+        <v>38</v>
       </c>
       <c r="J20" t="n">
-        <v>82.5</v>
+        <v>82.7</v>
       </c>
       <c r="K20" t="n">
         <v>0.459</v>
       </c>
       <c r="L20" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="M20" t="n">
-        <v>19.4</v>
+        <v>19.2</v>
       </c>
       <c r="N20" t="n">
-        <v>0.372</v>
+        <v>0.368</v>
       </c>
       <c r="O20" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="P20" t="n">
         <v>21.8</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.762</v>
+        <v>0.758</v>
       </c>
       <c r="R20" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="S20" t="n">
-        <v>32</v>
+        <v>32.1</v>
       </c>
       <c r="T20" t="n">
-        <v>43.4</v>
+        <v>43.6</v>
       </c>
       <c r="U20" t="n">
         <v>22.2</v>
       </c>
       <c r="V20" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="W20" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="X20" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Z20" t="n">
         <v>18.7</v>
@@ -4012,16 +4079,16 @@
         <v>99.59999999999999</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AD20" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AE20" t="n">
         <v>14</v>
       </c>
       <c r="AF20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG20" t="n">
         <v>14</v>
@@ -4030,10 +4097,10 @@
         <v>23</v>
       </c>
       <c r="AI20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AK20" t="n">
         <v>7</v>
@@ -4048,13 +4115,13 @@
         <v>4</v>
       </c>
       <c r="AO20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AP20" t="n">
         <v>20</v>
       </c>
       <c r="AQ20" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AR20" t="n">
         <v>10</v>
@@ -4063,7 +4130,7 @@
         <v>18</v>
       </c>
       <c r="AT20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AU20" t="n">
         <v>10</v>
@@ -4075,7 +4142,7 @@
         <v>25</v>
       </c>
       <c r="AX20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AY20" t="n">
         <v>28</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-3-2014-15</t>
+          <t>2015-04-03</t>
         </is>
       </c>
     </row>
@@ -4119,28 +4186,28 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E21" t="n">
         <v>14</v>
       </c>
       <c r="F21" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G21" t="n">
-        <v>0.184</v>
+        <v>0.187</v>
       </c>
       <c r="H21" t="n">
         <v>48.5</v>
       </c>
       <c r="I21" t="n">
-        <v>35.2</v>
+        <v>35.3</v>
       </c>
       <c r="J21" t="n">
         <v>82.40000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>0.427</v>
+        <v>0.428</v>
       </c>
       <c r="L21" t="n">
         <v>6.8</v>
@@ -4149,31 +4216,31 @@
         <v>19.8</v>
       </c>
       <c r="N21" t="n">
-        <v>0.344</v>
+        <v>0.345</v>
       </c>
       <c r="O21" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="P21" t="n">
         <v>18.9</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.77</v>
+        <v>0.768</v>
       </c>
       <c r="R21" t="n">
         <v>10.6</v>
       </c>
       <c r="S21" t="n">
-        <v>29.7</v>
+        <v>29.6</v>
       </c>
       <c r="T21" t="n">
-        <v>40.3</v>
+        <v>40.2</v>
       </c>
       <c r="U21" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="V21" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="W21" t="n">
         <v>7.1</v>
@@ -4182,10 +4249,10 @@
         <v>4.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Z21" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="AA21" t="n">
         <v>18.9</v>
@@ -4197,7 +4264,7 @@
         <v>-9.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AE21" t="n">
         <v>30</v>
@@ -4215,10 +4282,10 @@
         <v>28</v>
       </c>
       <c r="AJ21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL21" t="n">
         <v>21</v>
@@ -4227,7 +4294,7 @@
         <v>21</v>
       </c>
       <c r="AN21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO21" t="n">
         <v>29</v>
@@ -4260,7 +4327,7 @@
         <v>19</v>
       </c>
       <c r="AY21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ21" t="n">
         <v>26</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-3-2014-15</t>
+          <t>2015-04-03</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4368,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E22" t="n">
         <v>42</v>
       </c>
       <c r="F22" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G22" t="n">
-        <v>0.553</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H22" t="n">
         <v>48.4</v>
@@ -4322,7 +4389,7 @@
         <v>86.3</v>
       </c>
       <c r="K22" t="n">
-        <v>0.447</v>
+        <v>0.448</v>
       </c>
       <c r="L22" t="n">
         <v>7.6</v>
@@ -4331,7 +4398,7 @@
         <v>22.5</v>
       </c>
       <c r="N22" t="n">
-        <v>0.337</v>
+        <v>0.338</v>
       </c>
       <c r="O22" t="n">
         <v>18.7</v>
@@ -4340,7 +4407,7 @@
         <v>24.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.766</v>
+        <v>0.768</v>
       </c>
       <c r="R22" t="n">
         <v>12.6</v>
@@ -4355,13 +4422,13 @@
         <v>20.7</v>
       </c>
       <c r="V22" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W22" t="n">
         <v>7.2</v>
       </c>
       <c r="X22" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Y22" t="n">
         <v>4.6</v>
@@ -4373,31 +4440,31 @@
         <v>20.2</v>
       </c>
       <c r="AB22" t="n">
-        <v>103.5</v>
+        <v>103.6</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AE22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AF22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AG22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI22" t="n">
         <v>7</v>
       </c>
       <c r="AJ22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AK22" t="n">
         <v>18</v>
@@ -4436,7 +4503,7 @@
         <v>22</v>
       </c>
       <c r="AW22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX22" t="n">
         <v>6</v>
@@ -4451,7 +4518,7 @@
         <v>15</v>
       </c>
       <c r="BB22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BC22" t="n">
         <v>12</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-3-2014-15</t>
+          <t>2015-04-03</t>
         </is>
       </c>
     </row>
@@ -4486,52 +4553,52 @@
         <v>75</v>
       </c>
       <c r="E23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F23" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G23" t="n">
-        <v>0.307</v>
+        <v>0.293</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
       </c>
       <c r="I23" t="n">
-        <v>37.6</v>
+        <v>37.5</v>
       </c>
       <c r="J23" t="n">
-        <v>82.7</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>0.455</v>
+        <v>0.454</v>
       </c>
       <c r="L23" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="M23" t="n">
-        <v>19.5</v>
+        <v>19.3</v>
       </c>
       <c r="N23" t="n">
-        <v>0.348</v>
+        <v>0.349</v>
       </c>
       <c r="O23" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="P23" t="n">
         <v>19.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.73</v>
+        <v>0.732</v>
       </c>
       <c r="R23" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S23" t="n">
-        <v>31.6</v>
+        <v>31.7</v>
       </c>
       <c r="T23" t="n">
-        <v>41.4</v>
+        <v>41.5</v>
       </c>
       <c r="U23" t="n">
         <v>20.8</v>
@@ -4540,13 +4607,13 @@
         <v>14.9</v>
       </c>
       <c r="W23" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="X23" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="Z23" t="n">
         <v>21</v>
@@ -4555,13 +4622,13 @@
         <v>18</v>
       </c>
       <c r="AB23" t="n">
-        <v>96</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.8</v>
+        <v>-6.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="AE23" t="n">
         <v>26</v>
@@ -4579,10 +4646,10 @@
         <v>15</v>
       </c>
       <c r="AJ23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AL23" t="n">
         <v>22</v>
@@ -4591,7 +4658,7 @@
         <v>22</v>
       </c>
       <c r="AN23" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO23" t="n">
         <v>30</v>
@@ -4600,19 +4667,19 @@
         <v>29</v>
       </c>
       <c r="AQ23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AR23" t="n">
         <v>27</v>
       </c>
       <c r="AS23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT23" t="n">
         <v>25</v>
       </c>
       <c r="AU23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV23" t="n">
         <v>20</v>
@@ -4624,10 +4691,10 @@
         <v>29</v>
       </c>
       <c r="AY23" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AZ23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA23" t="n">
         <v>30</v>
@@ -4636,7 +4703,7 @@
         <v>25</v>
       </c>
       <c r="BC23" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-3-2014-15</t>
+          <t>2015-04-03</t>
         </is>
       </c>
     </row>
@@ -4755,7 +4822,7 @@
         <v>28</v>
       </c>
       <c r="AH24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI24" t="n">
         <v>30</v>
@@ -4767,7 +4834,7 @@
         <v>30</v>
       </c>
       <c r="AL24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AM24" t="n">
         <v>6</v>
@@ -4785,7 +4852,7 @@
         <v>30</v>
       </c>
       <c r="AR24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AS24" t="n">
         <v>26</v>
@@ -4794,7 +4861,7 @@
         <v>18</v>
       </c>
       <c r="AU24" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AV24" t="n">
         <v>30</v>
@@ -4806,13 +4873,13 @@
         <v>4</v>
       </c>
       <c r="AY24" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AZ24" t="n">
         <v>24</v>
       </c>
       <c r="BA24" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BB24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-3-2014-15</t>
+          <t>2015-04-03</t>
         </is>
       </c>
     </row>
@@ -4937,16 +5004,16 @@
         <v>15</v>
       </c>
       <c r="AH25" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AI25" t="n">
         <v>4</v>
       </c>
       <c r="AJ25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AL25" t="n">
         <v>9</v>
@@ -4961,10 +5028,10 @@
         <v>20</v>
       </c>
       <c r="AP25" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR25" t="n">
         <v>14</v>
@@ -4973,19 +5040,19 @@
         <v>12</v>
       </c>
       <c r="AT25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU25" t="n">
         <v>27</v>
       </c>
       <c r="AV25" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY25" t="n">
         <v>5</v>
@@ -4994,10 +5061,10 @@
         <v>25</v>
       </c>
       <c r="BA25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BC25" t="n">
         <v>17</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-3-2014-15</t>
+          <t>2015-04-03</t>
         </is>
       </c>
     </row>
@@ -5029,28 +5096,28 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E26" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F26" t="n">
         <v>26</v>
       </c>
       <c r="G26" t="n">
-        <v>0.653</v>
+        <v>0.649</v>
       </c>
       <c r="H26" t="n">
         <v>48.5</v>
       </c>
       <c r="I26" t="n">
-        <v>38.6</v>
+        <v>38.5</v>
       </c>
       <c r="J26" t="n">
         <v>85.8</v>
       </c>
       <c r="K26" t="n">
-        <v>0.45</v>
+        <v>0.449</v>
       </c>
       <c r="L26" t="n">
         <v>10</v>
@@ -5062,19 +5129,19 @@
         <v>0.365</v>
       </c>
       <c r="O26" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="P26" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.799</v>
+        <v>0.797</v>
       </c>
       <c r="R26" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="S26" t="n">
-        <v>35.2</v>
+        <v>35.1</v>
       </c>
       <c r="T26" t="n">
         <v>45.9</v>
@@ -5083,10 +5150,10 @@
         <v>22</v>
       </c>
       <c r="V26" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="W26" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="X26" t="n">
         <v>4.6</v>
@@ -5095,28 +5162,28 @@
         <v>3.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>18.1</v>
+        <v>18.2</v>
       </c>
       <c r="AA26" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="AB26" t="n">
         <v>102.9</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="AE26" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AF26" t="n">
         <v>5</v>
       </c>
       <c r="AG26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH26" t="n">
         <v>10</v>
@@ -5149,7 +5216,7 @@
         <v>1</v>
       </c>
       <c r="AR26" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AS26" t="n">
         <v>1</v>
@@ -5167,7 +5234,7 @@
         <v>27</v>
       </c>
       <c r="AX26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY26" t="n">
         <v>3</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-3-2014-15</t>
+          <t>2015-04-03</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E27" t="n">
         <v>26</v>
       </c>
       <c r="F27" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G27" t="n">
-        <v>0.347</v>
+        <v>0.351</v>
       </c>
       <c r="H27" t="n">
         <v>48.5</v>
@@ -5244,52 +5311,52 @@
         <v>0.339</v>
       </c>
       <c r="O27" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="P27" t="n">
         <v>28.9</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.772</v>
+        <v>0.775</v>
       </c>
       <c r="R27" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="S27" t="n">
         <v>33.4</v>
       </c>
       <c r="T27" t="n">
-        <v>44.5</v>
+        <v>44.6</v>
       </c>
       <c r="U27" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="V27" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="W27" t="n">
         <v>6.6</v>
       </c>
       <c r="X27" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Y27" t="n">
         <v>6.3</v>
       </c>
       <c r="Z27" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AA27" t="n">
         <v>23.8</v>
       </c>
       <c r="AB27" t="n">
-        <v>100.9</v>
+        <v>101</v>
       </c>
       <c r="AC27" t="n">
         <v>-4</v>
       </c>
       <c r="AD27" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="AE27" t="n">
         <v>25</v>
@@ -5304,13 +5371,13 @@
         <v>10</v>
       </c>
       <c r="AI27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AJ27" t="n">
         <v>28</v>
       </c>
       <c r="AK27" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL27" t="n">
         <v>28</v>
@@ -5328,16 +5395,16 @@
         <v>1</v>
       </c>
       <c r="AQ27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AR27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AS27" t="n">
         <v>9</v>
       </c>
       <c r="AT27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AU27" t="n">
         <v>28</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-3-2014-15</t>
+          <t>2015-04-03</t>
         </is>
       </c>
     </row>
@@ -5408,10 +5475,10 @@
         <v>48.7</v>
       </c>
       <c r="I28" t="n">
-        <v>38.8</v>
+        <v>38.7</v>
       </c>
       <c r="J28" t="n">
-        <v>83.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K28" t="n">
         <v>0.463</v>
@@ -5420,10 +5487,10 @@
         <v>8.300000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="N28" t="n">
-        <v>0.366</v>
+        <v>0.367</v>
       </c>
       <c r="O28" t="n">
         <v>16.9</v>
@@ -5432,10 +5499,10 @@
         <v>21.7</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.779</v>
+        <v>0.778</v>
       </c>
       <c r="R28" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="S28" t="n">
         <v>33.8</v>
@@ -5444,34 +5511,34 @@
         <v>43.7</v>
       </c>
       <c r="U28" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="V28" t="n">
         <v>13.9</v>
       </c>
       <c r="W28" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="X28" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y28" t="n">
         <v>4.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="AA28" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AB28" t="n">
-        <v>102.9</v>
+        <v>102.6</v>
       </c>
       <c r="AC28" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="AE28" t="n">
         <v>6</v>
@@ -5486,13 +5553,13 @@
         <v>1</v>
       </c>
       <c r="AI28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ28" t="n">
         <v>12</v>
       </c>
       <c r="AK28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AL28" t="n">
         <v>12</v>
@@ -5507,10 +5574,10 @@
         <v>14</v>
       </c>
       <c r="AP28" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AR28" t="n">
         <v>26</v>
@@ -5519,10 +5586,10 @@
         <v>8</v>
       </c>
       <c r="AT28" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV28" t="n">
         <v>11</v>
@@ -5537,7 +5604,7 @@
         <v>9</v>
       </c>
       <c r="AZ28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA28" t="n">
         <v>20</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-3-2014-15</t>
+          <t>2015-04-03</t>
         </is>
       </c>
     </row>
@@ -5575,34 +5642,34 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E29" t="n">
         <v>45</v>
       </c>
       <c r="F29" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G29" t="n">
-        <v>0.592</v>
+        <v>0.6</v>
       </c>
       <c r="H29" t="n">
         <v>48.4</v>
       </c>
       <c r="I29" t="n">
-        <v>38</v>
+        <v>37.9</v>
       </c>
       <c r="J29" t="n">
         <v>83.40000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>0.456</v>
+        <v>0.455</v>
       </c>
       <c r="L29" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="M29" t="n">
-        <v>25</v>
+        <v>24.9</v>
       </c>
       <c r="N29" t="n">
         <v>0.353</v>
@@ -5614,13 +5681,13 @@
         <v>24.8</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.787</v>
+        <v>0.788</v>
       </c>
       <c r="R29" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="S29" t="n">
-        <v>30.6</v>
+        <v>30.7</v>
       </c>
       <c r="T29" t="n">
         <v>41.4</v>
@@ -5629,49 +5696,49 @@
         <v>20.9</v>
       </c>
       <c r="V29" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="W29" t="n">
         <v>7.5</v>
       </c>
       <c r="X29" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Y29" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Z29" t="n">
         <v>20.9</v>
       </c>
       <c r="AA29" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>104.3</v>
+        <v>104.2</v>
       </c>
       <c r="AC29" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AD29" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AE29" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI29" t="n">
         <v>11</v>
       </c>
-      <c r="AF29" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH29" t="n">
+      <c r="AJ29" t="n">
         <v>15</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>14</v>
       </c>
       <c r="AK29" t="n">
         <v>12</v>
@@ -5680,22 +5747,22 @@
         <v>8</v>
       </c>
       <c r="AM29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AN29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO29" t="n">
         <v>4</v>
       </c>
       <c r="AP29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ29" t="n">
         <v>2</v>
       </c>
       <c r="AR29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS29" t="n">
         <v>27</v>
@@ -5713,7 +5780,7 @@
         <v>17</v>
       </c>
       <c r="AX29" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AY29" t="n">
         <v>19</v>
@@ -5722,13 +5789,13 @@
         <v>17</v>
       </c>
       <c r="BA29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BB29" t="n">
         <v>4</v>
       </c>
       <c r="BC29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-3-2014-15</t>
+          <t>2015-04-03</t>
         </is>
       </c>
     </row>
@@ -5835,10 +5902,10 @@
         <v>0.1</v>
       </c>
       <c r="AD30" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE30" t="n">
         <v>17</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>18</v>
       </c>
       <c r="AF30" t="n">
         <v>18</v>
@@ -5871,10 +5938,10 @@
         <v>15</v>
       </c>
       <c r="AP30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AR30" t="n">
         <v>4</v>
@@ -5889,28 +5956,28 @@
         <v>30</v>
       </c>
       <c r="AV30" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW30" t="n">
         <v>18</v>
       </c>
       <c r="AX30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY30" t="n">
         <v>13</v>
       </c>
       <c r="AZ30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA30" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BB30" t="n">
         <v>27</v>
       </c>
       <c r="BC30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-3-2014-15</t>
+          <t>2015-04-03</t>
         </is>
       </c>
     </row>
@@ -5939,25 +6006,25 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E31" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F31" t="n">
         <v>33</v>
       </c>
       <c r="G31" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H31" t="n">
         <v>48.5</v>
       </c>
       <c r="I31" t="n">
-        <v>38.2</v>
+        <v>38.1</v>
       </c>
       <c r="J31" t="n">
-        <v>82.5</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K31" t="n">
         <v>0.463</v>
@@ -5969,16 +6036,16 @@
         <v>16.6</v>
       </c>
       <c r="N31" t="n">
-        <v>0.358</v>
+        <v>0.357</v>
       </c>
       <c r="O31" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="P31" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.741</v>
+        <v>0.742</v>
       </c>
       <c r="R31" t="n">
         <v>10.4</v>
@@ -5990,10 +6057,10 @@
         <v>44.3</v>
       </c>
       <c r="U31" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="V31" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W31" t="n">
         <v>7.4</v>
@@ -6008,16 +6075,16 @@
         <v>21</v>
       </c>
       <c r="AA31" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AB31" t="n">
         <v>98.40000000000001</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AE31" t="n">
         <v>12</v>
@@ -6035,13 +6102,13 @@
         <v>9</v>
       </c>
       <c r="AJ31" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AK31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL31" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AM31" t="n">
         <v>27</v>
@@ -6050,10 +6117,10 @@
         <v>9</v>
       </c>
       <c r="AO31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP31" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AQ31" t="n">
         <v>23</v>
@@ -6062,7 +6129,7 @@
         <v>20</v>
       </c>
       <c r="AS31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT31" t="n">
         <v>10</v>
@@ -6077,13 +6144,13 @@
         <v>20</v>
       </c>
       <c r="AX31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA31" t="n">
         <v>21</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-3-2014-15</t>
+          <t>2015-04-03</t>
         </is>
       </c>
     </row>
